--- a/results/job_matches_2026-07-19.xlsx
+++ b/results/job_matches_2026-07-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
+          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
+          <t>Databricks Data Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d92e12b65009362</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Integration Services Engineer</t>
+          <t>Databricks Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=cde8aceb659b7851</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Databricks Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=323b12004fd1fa17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Databricks Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,1442 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ddde05a799d0e50f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e54319cb7bfa838</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9892f5c3468ad608</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73a45b153230dc4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d71599297538b2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=432634e664780bce</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a64444682287c104</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=530638f3e1daf38d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14c62fa36d929316</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70f14cf3390679d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24044e6dca60597c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0eddd74c6020e60d</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=882a8e1d53732532</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43664ccf89ac9845</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75900edce4a3140c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61bd23c88ade521e</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c70c7100dc6891fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f9e9959edbf67f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eba7cfb89bad5673</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32643431aa45b014</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54b8c2e010e3c30e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b3cee7777b3be3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=934e77f21c46da71</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bdb0a98c0d3edce</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7314558051799a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=977374dcac480610</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07bcb5ba3fa3bcdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2b3bad974d3cce6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbb994ffce3e09da</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d8b975518822603</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Integration Services Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Toll Brothers</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fort Washington, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D40" t="n">
         <v>10.4</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01965fadde442044</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da13b00a43473377</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78531d1019f4b8d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b47fc7d04ca49300</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42e4270a4174f66d</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16c9e1dd0a8fd75b</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09676da45784cdfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c910ea741626def</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b63b1ead449795e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=365840ba6be285e4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-19.xlsx
+++ b/results/job_matches_2026-07-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DEV OPS ENGINEER IV</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Envision Healthcare</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234470a5d086eaec</t>
+          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
+          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
+          <t>Databricks Data Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d92e12b65009362</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d92e12b65009362</t>
+          <t>https://www.indeed.com/viewjob?jk=cde8aceb659b7851</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde8aceb659b7851</t>
+          <t>https://www.indeed.com/viewjob?jk=323b12004fd1fa17</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323b12004fd1fa17</t>
+          <t>https://www.indeed.com/viewjob?jk=ddde05a799d0e50f</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddde05a799d0e50f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e54319cb7bfa838</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e54319cb7bfa838</t>
+          <t>https://www.indeed.com/viewjob?jk=9892f5c3468ad608</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9892f5c3468ad608</t>
+          <t>https://www.indeed.com/viewjob?jk=73a45b153230dc4d</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a45b153230dc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d71599297538b2a</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d71599297538b2a</t>
+          <t>https://www.indeed.com/viewjob?jk=432634e664780bce</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432634e664780bce</t>
+          <t>https://www.indeed.com/viewjob?jk=a64444682287c104</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64444682287c104</t>
+          <t>https://www.indeed.com/viewjob?jk=530638f3e1daf38d</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530638f3e1daf38d</t>
+          <t>https://www.indeed.com/viewjob?jk=14c62fa36d929316</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c62fa36d929316</t>
+          <t>https://www.indeed.com/viewjob?jk=70f14cf3390679d5</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f14cf3390679d5</t>
+          <t>https://www.indeed.com/viewjob?jk=24044e6dca60597c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24044e6dca60597c</t>
+          <t>https://www.indeed.com/viewjob?jk=0eddd74c6020e60d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eddd74c6020e60d</t>
+          <t>https://www.indeed.com/viewjob?jk=882a8e1d53732532</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882a8e1d53732532</t>
+          <t>https://www.indeed.com/viewjob?jk=43664ccf89ac9845</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43664ccf89ac9845</t>
+          <t>https://www.indeed.com/viewjob?jk=75900edce4a3140c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75900edce4a3140c</t>
+          <t>https://www.indeed.com/viewjob?jk=61bd23c88ade521e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bd23c88ade521e</t>
+          <t>https://www.indeed.com/viewjob?jk=c70c7100dc6891fd</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70c7100dc6891fd</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9e9959edbf67f2</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9e9959edbf67f2</t>
+          <t>https://www.indeed.com/viewjob?jk=eba7cfb89bad5673</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba7cfb89bad5673</t>
+          <t>https://www.indeed.com/viewjob?jk=32643431aa45b014</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32643431aa45b014</t>
+          <t>https://www.indeed.com/viewjob?jk=54b8c2e010e3c30e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b8c2e010e3c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3cee7777b3be3e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cee7777b3be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=934e77f21c46da71</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934e77f21c46da71</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdb0a98c0d3edce</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdb0a98c0d3edce</t>
+          <t>https://www.indeed.com/viewjob?jk=b7314558051799a4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7314558051799a4</t>
+          <t>https://www.indeed.com/viewjob?jk=977374dcac480610</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977374dcac480610</t>
+          <t>https://www.indeed.com/viewjob?jk=07bcb5ba3fa3bcdf</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07bcb5ba3fa3bcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b3bad974d3cce6</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b3bad974d3cce6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb994ffce3e09da</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb994ffce3e09da</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8b975518822603</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer II</t>
+          <t>Integration Services Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8b975518822603</t>
+          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Integration Services Engineer</t>
+          <t>Applied AI Engineer I</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=01965fadde442044</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
+          <t>Applied AI Engineer I</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=da13b00a43473377</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01965fadde442044</t>
+          <t>https://www.indeed.com/viewjob?jk=78531d1019f4b8d6</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da13b00a43473377</t>
+          <t>https://www.indeed.com/viewjob?jk=b47fc7d04ca49300</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78531d1019f4b8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=42e4270a4174f66d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Applied AI Engineer I</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47fc7d04ca49300</t>
+          <t>https://www.indeed.com/viewjob?jk=16c9e1dd0a8fd75b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Applied AI Engineer I</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e4270a4174f66d</t>
+          <t>https://www.indeed.com/viewjob?jk=09676da45784cdfc</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c9e1dd0a8fd75b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c910ea741626def</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09676da45784cdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b63b1ead449795e5</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2105,76 +2105,6 @@
         </is>
       </c>
       <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c910ea741626def</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b63b1ead449795e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=365840ba6be285e4</t>
         </is>

--- a/results/job_matches_2026-07-19.xlsx
+++ b/results/job_matches_2026-07-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
+          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
+          <t>Databricks Data Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d92e12b65009362</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d92e12b65009362</t>
+          <t>https://www.indeed.com/viewjob?jk=cde8aceb659b7851</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde8aceb659b7851</t>
+          <t>https://www.indeed.com/viewjob?jk=323b12004fd1fa17</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323b12004fd1fa17</t>
+          <t>https://www.indeed.com/viewjob?jk=ddde05a799d0e50f</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddde05a799d0e50f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e54319cb7bfa838</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e54319cb7bfa838</t>
+          <t>https://www.indeed.com/viewjob?jk=9892f5c3468ad608</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9892f5c3468ad608</t>
+          <t>https://www.indeed.com/viewjob?jk=73a45b153230dc4d</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a45b153230dc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d71599297538b2a</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d71599297538b2a</t>
+          <t>https://www.indeed.com/viewjob?jk=432634e664780bce</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432634e664780bce</t>
+          <t>https://www.indeed.com/viewjob?jk=a64444682287c104</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64444682287c104</t>
+          <t>https://www.indeed.com/viewjob?jk=530638f3e1daf38d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530638f3e1daf38d</t>
+          <t>https://www.indeed.com/viewjob?jk=14c62fa36d929316</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c62fa36d929316</t>
+          <t>https://www.indeed.com/viewjob?jk=70f14cf3390679d5</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f14cf3390679d5</t>
+          <t>https://www.indeed.com/viewjob?jk=24044e6dca60597c</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24044e6dca60597c</t>
+          <t>https://www.indeed.com/viewjob?jk=0eddd74c6020e60d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eddd74c6020e60d</t>
+          <t>https://www.indeed.com/viewjob?jk=882a8e1d53732532</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882a8e1d53732532</t>
+          <t>https://www.indeed.com/viewjob?jk=43664ccf89ac9845</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43664ccf89ac9845</t>
+          <t>https://www.indeed.com/viewjob?jk=75900edce4a3140c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75900edce4a3140c</t>
+          <t>https://www.indeed.com/viewjob?jk=61bd23c88ade521e</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bd23c88ade521e</t>
+          <t>https://www.indeed.com/viewjob?jk=c70c7100dc6891fd</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70c7100dc6891fd</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9e9959edbf67f2</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9e9959edbf67f2</t>
+          <t>https://www.indeed.com/viewjob?jk=eba7cfb89bad5673</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba7cfb89bad5673</t>
+          <t>https://www.indeed.com/viewjob?jk=32643431aa45b014</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32643431aa45b014</t>
+          <t>https://www.indeed.com/viewjob?jk=54b8c2e010e3c30e</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b8c2e010e3c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3cee7777b3be3e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cee7777b3be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=934e77f21c46da71</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934e77f21c46da71</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdb0a98c0d3edce</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdb0a98c0d3edce</t>
+          <t>https://www.indeed.com/viewjob?jk=b7314558051799a4</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7314558051799a4</t>
+          <t>https://www.indeed.com/viewjob?jk=977374dcac480610</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977374dcac480610</t>
+          <t>https://www.indeed.com/viewjob?jk=07bcb5ba3fa3bcdf</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07bcb5ba3fa3bcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b3bad974d3cce6</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b3bad974d3cce6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb994ffce3e09da</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb994ffce3e09da</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8b975518822603</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer II</t>
+          <t>Integration Services Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8b975518822603</t>
+          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Integration Services Engineer</t>
+          <t>Applied AI Engineer I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=01965fadde442044</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01965fadde442044</t>
+          <t>https://www.indeed.com/viewjob?jk=da13b00a43473377</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da13b00a43473377</t>
+          <t>https://www.indeed.com/viewjob?jk=78531d1019f4b8d6</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78531d1019f4b8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b47fc7d04ca49300</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47fc7d04ca49300</t>
+          <t>https://www.indeed.com/viewjob?jk=42e4270a4174f66d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Applied AI Engineer I</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e4270a4174f66d</t>
+          <t>https://www.indeed.com/viewjob?jk=16c9e1dd0a8fd75b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c9e1dd0a8fd75b</t>
+          <t>https://www.indeed.com/viewjob?jk=09676da45784cdfc</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09676da45784cdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c910ea741626def</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c910ea741626def</t>
+          <t>https://www.indeed.com/viewjob?jk=b63b1ead449795e5</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2070,41 +2070,6 @@
         </is>
       </c>
       <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b63b1ead449795e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=365840ba6be285e4</t>
         </is>

--- a/results/job_matches_2026-07-19.xlsx
+++ b/results/job_matches_2026-07-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
+          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
+          <t>Databricks Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d92e12b65009362</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d92e12b65009362</t>
+          <t>https://www.indeed.com/viewjob?jk=cde8aceb659b7851</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde8aceb659b7851</t>
+          <t>https://www.indeed.com/viewjob?jk=323b12004fd1fa17</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323b12004fd1fa17</t>
+          <t>https://www.indeed.com/viewjob?jk=ddde05a799d0e50f</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddde05a799d0e50f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e54319cb7bfa838</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e54319cb7bfa838</t>
+          <t>https://www.indeed.com/viewjob?jk=9892f5c3468ad608</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9892f5c3468ad608</t>
+          <t>https://www.indeed.com/viewjob?jk=73a45b153230dc4d</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a45b153230dc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d71599297538b2a</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d71599297538b2a</t>
+          <t>https://www.indeed.com/viewjob?jk=432634e664780bce</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432634e664780bce</t>
+          <t>https://www.indeed.com/viewjob?jk=a64444682287c104</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64444682287c104</t>
+          <t>https://www.indeed.com/viewjob?jk=530638f3e1daf38d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530638f3e1daf38d</t>
+          <t>https://www.indeed.com/viewjob?jk=14c62fa36d929316</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c62fa36d929316</t>
+          <t>https://www.indeed.com/viewjob?jk=70f14cf3390679d5</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f14cf3390679d5</t>
+          <t>https://www.indeed.com/viewjob?jk=24044e6dca60597c</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24044e6dca60597c</t>
+          <t>https://www.indeed.com/viewjob?jk=0eddd74c6020e60d</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eddd74c6020e60d</t>
+          <t>https://www.indeed.com/viewjob?jk=882a8e1d53732532</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882a8e1d53732532</t>
+          <t>https://www.indeed.com/viewjob?jk=43664ccf89ac9845</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43664ccf89ac9845</t>
+          <t>https://www.indeed.com/viewjob?jk=75900edce4a3140c</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75900edce4a3140c</t>
+          <t>https://www.indeed.com/viewjob?jk=61bd23c88ade521e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bd23c88ade521e</t>
+          <t>https://www.indeed.com/viewjob?jk=c70c7100dc6891fd</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70c7100dc6891fd</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9e9959edbf67f2</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9e9959edbf67f2</t>
+          <t>https://www.indeed.com/viewjob?jk=eba7cfb89bad5673</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba7cfb89bad5673</t>
+          <t>https://www.indeed.com/viewjob?jk=32643431aa45b014</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32643431aa45b014</t>
+          <t>https://www.indeed.com/viewjob?jk=54b8c2e010e3c30e</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b8c2e010e3c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3cee7777b3be3e</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cee7777b3be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=934e77f21c46da71</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934e77f21c46da71</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdb0a98c0d3edce</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdb0a98c0d3edce</t>
+          <t>https://www.indeed.com/viewjob?jk=b7314558051799a4</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7314558051799a4</t>
+          <t>https://www.indeed.com/viewjob?jk=977374dcac480610</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977374dcac480610</t>
+          <t>https://www.indeed.com/viewjob?jk=07bcb5ba3fa3bcdf</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07bcb5ba3fa3bcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b3bad974d3cce6</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b3bad974d3cce6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb994ffce3e09da</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb994ffce3e09da</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8b975518822603</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer II</t>
+          <t>Integration Services Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8b975518822603</t>
+          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Integration Services Engineer</t>
+          <t>Applied AI Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=01965fadde442044</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01965fadde442044</t>
+          <t>https://www.indeed.com/viewjob?jk=da13b00a43473377</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da13b00a43473377</t>
+          <t>https://www.indeed.com/viewjob?jk=78531d1019f4b8d6</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78531d1019f4b8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b47fc7d04ca49300</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47fc7d04ca49300</t>
+          <t>https://www.indeed.com/viewjob?jk=42e4270a4174f66d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Applied AI Engineer I</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e4270a4174f66d</t>
+          <t>https://www.indeed.com/viewjob?jk=16c9e1dd0a8fd75b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c9e1dd0a8fd75b</t>
+          <t>https://www.indeed.com/viewjob?jk=09676da45784cdfc</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09676da45784cdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c910ea741626def</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c910ea741626def</t>
+          <t>https://www.indeed.com/viewjob?jk=b63b1ead449795e5</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2035,41 +2035,6 @@
         </is>
       </c>
       <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b63b1ead449795e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=365840ba6be285e4</t>
         </is>

--- a/results/job_matches_2026-07-19.xlsx
+++ b/results/job_matches_2026-07-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
+          <t>Databricks Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d92e12b65009362</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d92e12b65009362</t>
+          <t>https://www.indeed.com/viewjob?jk=cde8aceb659b7851</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde8aceb659b7851</t>
+          <t>https://www.indeed.com/viewjob?jk=323b12004fd1fa17</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323b12004fd1fa17</t>
+          <t>https://www.indeed.com/viewjob?jk=ddde05a799d0e50f</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddde05a799d0e50f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e54319cb7bfa838</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e54319cb7bfa838</t>
+          <t>https://www.indeed.com/viewjob?jk=9892f5c3468ad608</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9892f5c3468ad608</t>
+          <t>https://www.indeed.com/viewjob?jk=73a45b153230dc4d</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a45b153230dc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d71599297538b2a</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d71599297538b2a</t>
+          <t>https://www.indeed.com/viewjob?jk=432634e664780bce</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432634e664780bce</t>
+          <t>https://www.indeed.com/viewjob?jk=a64444682287c104</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64444682287c104</t>
+          <t>https://www.indeed.com/viewjob?jk=530638f3e1daf38d</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530638f3e1daf38d</t>
+          <t>https://www.indeed.com/viewjob?jk=14c62fa36d929316</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c62fa36d929316</t>
+          <t>https://www.indeed.com/viewjob?jk=70f14cf3390679d5</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f14cf3390679d5</t>
+          <t>https://www.indeed.com/viewjob?jk=24044e6dca60597c</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24044e6dca60597c</t>
+          <t>https://www.indeed.com/viewjob?jk=0eddd74c6020e60d</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eddd74c6020e60d</t>
+          <t>https://www.indeed.com/viewjob?jk=882a8e1d53732532</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882a8e1d53732532</t>
+          <t>https://www.indeed.com/viewjob?jk=43664ccf89ac9845</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43664ccf89ac9845</t>
+          <t>https://www.indeed.com/viewjob?jk=75900edce4a3140c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75900edce4a3140c</t>
+          <t>https://www.indeed.com/viewjob?jk=61bd23c88ade521e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bd23c88ade521e</t>
+          <t>https://www.indeed.com/viewjob?jk=c70c7100dc6891fd</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70c7100dc6891fd</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9e9959edbf67f2</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9e9959edbf67f2</t>
+          <t>https://www.indeed.com/viewjob?jk=eba7cfb89bad5673</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba7cfb89bad5673</t>
+          <t>https://www.indeed.com/viewjob?jk=32643431aa45b014</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32643431aa45b014</t>
+          <t>https://www.indeed.com/viewjob?jk=54b8c2e010e3c30e</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b8c2e010e3c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3cee7777b3be3e</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cee7777b3be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=934e77f21c46da71</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934e77f21c46da71</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdb0a98c0d3edce</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdb0a98c0d3edce</t>
+          <t>https://www.indeed.com/viewjob?jk=b7314558051799a4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7314558051799a4</t>
+          <t>https://www.indeed.com/viewjob?jk=977374dcac480610</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977374dcac480610</t>
+          <t>https://www.indeed.com/viewjob?jk=07bcb5ba3fa3bcdf</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07bcb5ba3fa3bcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b3bad974d3cce6</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b3bad974d3cce6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb994ffce3e09da</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb994ffce3e09da</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8b975518822603</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer II</t>
+          <t>Integration Services Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8b975518822603</t>
+          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Integration Services Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=1d44fe55ea5358c0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Applied AI Engineer I</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01965fadde442044</t>
+          <t>https://www.indeed.com/viewjob?jk=90259e539c619c3a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Applied AI Engineer I</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da13b00a43473377</t>
+          <t>https://www.indeed.com/viewjob?jk=3745a4ff718ce48f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Applied AI Engineer I</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78531d1019f4b8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=22d8e6b9fcebf351</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Applied AI Engineer I</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47fc7d04ca49300</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f10acc01735c15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Applied AI Engineer I</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e4270a4174f66d</t>
+          <t>https://www.indeed.com/viewjob?jk=17631ca9c910c51a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16c9e1dd0a8fd75b</t>
+          <t>https://www.indeed.com/viewjob?jk=23567ec8e77ea65b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09676da45784cdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=c9eef8d0c0765532</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c910ea741626def</t>
+          <t>https://www.indeed.com/viewjob?jk=a7accd1dc6af81c7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,50 +1991,1695 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63b1ead449795e5</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0deb86a680c0de</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=058219ed3cf271c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5960061ff2c14124</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efcd71145988051b</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf1bb8ce02c165ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb37d33702c42988</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8907c281b0e38f47</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=beebf422d6142215</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=902226c872c65d76</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f9e362ca7c899ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b51fccdaf83e7a45</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f65723c1b0cc42c</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4e1a7479e3c6d75</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e5cc50e4e4adbf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc11fd2fdbc68b19</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ec1122013ede43c</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26b56b67b5618828</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfb2d0031f21849e</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3273f104f39f71f</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DE, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be4545129fbd8171</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=893ba2b33005a817</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5936c0fe3cc1d810</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bde6bd7b18d8094e</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93d82d34c4d4d9f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7ae845d5455b185</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c3932d8bffff36f</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d933358595b905a</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44af55d588aefe42</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32914027e92100b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75736eaa5f691233</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c7df172e8ccdf8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fc9672f510c9438</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91dfbf05e523fa6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NH, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b56f3704d5d66e0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d139d3986b9afd07</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94c0dc12ce6825fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SD, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa84bf5bd57711a</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ef90d605a9f8edf</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc1ceec59ac88d89</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01965fadde442044</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da13b00a43473377</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78531d1019f4b8d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b47fc7d04ca49300</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer I</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42e4270a4174f66d</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>Applied AI Engineer II</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16c9e1dd0a8fd75b</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09676da45784cdfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c910ea741626def</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b63b1ead449795e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
         <is>
           <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=365840ba6be285e4</t>
         </is>

--- a/results/job_matches_2026-07-19.xlsx
+++ b/results/job_matches_2026-07-19.xlsx
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer II</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d92e12b65009362</t>
+          <t>https://www.indeed.com/viewjob?jk=0162590b4bca3d10</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde8aceb659b7851</t>
+          <t>https://www.indeed.com/viewjob?jk=9d92e12b65009362</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323b12004fd1fa17</t>
+          <t>https://www.indeed.com/viewjob?jk=cde8aceb659b7851</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddde05a799d0e50f</t>
+          <t>https://www.indeed.com/viewjob?jk=323b12004fd1fa17</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e54319cb7bfa838</t>
+          <t>https://www.indeed.com/viewjob?jk=ddde05a799d0e50f</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9892f5c3468ad608</t>
+          <t>https://www.indeed.com/viewjob?jk=6e54319cb7bfa838</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73a45b153230dc4d</t>
+          <t>https://www.indeed.com/viewjob?jk=9892f5c3468ad608</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d71599297538b2a</t>
+          <t>https://www.indeed.com/viewjob?jk=73a45b153230dc4d</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432634e664780bce</t>
+          <t>https://www.indeed.com/viewjob?jk=1d71599297538b2a</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64444682287c104</t>
+          <t>https://www.indeed.com/viewjob?jk=432634e664780bce</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530638f3e1daf38d</t>
+          <t>https://www.indeed.com/viewjob?jk=a64444682287c104</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c62fa36d929316</t>
+          <t>https://www.indeed.com/viewjob?jk=530638f3e1daf38d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f14cf3390679d5</t>
+          <t>https://www.indeed.com/viewjob?jk=14c62fa36d929316</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24044e6dca60597c</t>
+          <t>https://www.indeed.com/viewjob?jk=70f14cf3390679d5</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eddd74c6020e60d</t>
+          <t>https://www.indeed.com/viewjob?jk=24044e6dca60597c</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882a8e1d53732532</t>
+          <t>https://www.indeed.com/viewjob?jk=0eddd74c6020e60d</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43664ccf89ac9845</t>
+          <t>https://www.indeed.com/viewjob?jk=882a8e1d53732532</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75900edce4a3140c</t>
+          <t>https://www.indeed.com/viewjob?jk=43664ccf89ac9845</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bd23c88ade521e</t>
+          <t>https://www.indeed.com/viewjob?jk=75900edce4a3140c</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70c7100dc6891fd</t>
+          <t>https://www.indeed.com/viewjob?jk=61bd23c88ade521e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f9e9959edbf67f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c70c7100dc6891fd</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba7cfb89bad5673</t>
+          <t>https://www.indeed.com/viewjob?jk=7f9e9959edbf67f2</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32643431aa45b014</t>
+          <t>https://www.indeed.com/viewjob?jk=eba7cfb89bad5673</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54b8c2e010e3c30e</t>
+          <t>https://www.indeed.com/viewjob?jk=32643431aa45b014</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3cee7777b3be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=54b8c2e010e3c30e</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934e77f21c46da71</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3cee7777b3be3e</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdb0a98c0d3edce</t>
+          <t>https://www.indeed.com/viewjob?jk=934e77f21c46da71</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7314558051799a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdb0a98c0d3edce</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977374dcac480610</t>
+          <t>https://www.indeed.com/viewjob?jk=b7314558051799a4</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07bcb5ba3fa3bcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=977374dcac480610</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b3bad974d3cce6</t>
+          <t>https://www.indeed.com/viewjob?jk=07bcb5ba3fa3bcdf</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb994ffce3e09da</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b3bad974d3cce6</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8b975518822603</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb994ffce3e09da</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Integration Services Engineer</t>
+          <t>Databricks Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8b975518822603</t>
         </is>
       </c>
     </row>
